--- a/PCB/PickAndPlace_XAI_MB.xlsx
+++ b/PCB/PickAndPlace_XAI_MB.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_09_29" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_10_14" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
   <si>
     <t>Designator</t>
   </si>
@@ -146,27 +146,6 @@
   </si>
   <si>
     <t>No</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>SI1967DH-T1-GE3</t>
-  </si>
-  <si>
-    <t>SOT-363_L2.0-W1.3-P0.65-LS2.1-BL</t>
-  </si>
-  <si>
-    <t>34.29mm</t>
-  </si>
-  <si>
-    <t>-22.606mm</t>
-  </si>
-  <si>
-    <t>35.28mm</t>
-  </si>
-  <si>
-    <t>-23.256mm</t>
   </si>
   <si>
     <t>RN1</t>
@@ -588,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -858,116 +837,69 @@
         <v>51</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
       </c>
       <c r="L6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M6" t="s">
         <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="O6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" t="s">
         <v>56</v>
       </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
       </c>
       <c r="L7">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M7" t="s">
         <v>22</v>
       </c>
       <c r="N7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8">
-        <v>16</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
